--- a/平台部署时间进度表_详细版_6月5日-30日.xlsx
+++ b/平台部署时间进度表_详细版_6月5日-30日.xlsx
@@ -524,10 +524,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>统计时间：2026年6月5日 | 总模块：18个 | 已完成：12个 | 进行中：2个 | 待开始：2个 | 等待备案：1个 | 规划中：1个</t>
-        </is>
-      </c>
-    </row>
+          <t>统计时间：2026年6月12日 ｜ 总模块：18个 ｜ 已完成：16个 ｜ 进行中：1个 ｜ 待开始：1个 ｜ 等待备案：0个 ｜ 规划中：0个</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -914,12 +915,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>🔄 进行中</t>
+          <t>✔ 已完成</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>预计6月6日</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -929,7 +930,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>商户可在后台修改红框尺寸</t>
+          <t>商户后台可修改红框尺寸</t>
         </is>
       </c>
     </row>
@@ -941,12 +942,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>🔄 进行中</t>
+          <t>✔ 已完成</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>预计6月6日</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -956,7 +957,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>查看投诉列表、处理投诉</t>
+          <t>投诉列表+详情处理完整实现</t>
         </is>
       </c>
     </row>
@@ -968,12 +969,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>⏸ 等待审核</t>
+          <t>✔ 已通过</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>预计6月8日</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -983,7 +984,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>备案审核中，预计6月8日通过</t>
+          <t>已上线 www.zhibanhome.com</t>
         </is>
       </c>
     </row>
@@ -995,12 +996,12 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>⏳ 待开始</t>
+          <t>🔄 进行中</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>6月10日-11日</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1010,7 +1011,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>SQLite数据迁移</t>
+          <t>服务器已升级4核8G，具备迁移条件</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1028,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>6月12日-13日</t>
+          <t>预计6月15-16日</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1049,12 +1050,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>📋 规划中</t>
+          <t>✔ 已完成</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>6月15日-18日</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1064,10 +1065,11 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>优化客户修改尺寸的体验</t>
-        </is>
-      </c>
-    </row>
+          <t>下单页Canvas交互+版类效果预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
@@ -1143,7 +1145,8 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>已完成
+ECS已升级4核8G，OSS/SSL/Nginx已就绪</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1185,8 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>确认服务器资源充足</t>
+          <t>进行中
+服务器升级完成，开始迁移</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1225,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>保留SQLite作为回退备份</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1265,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>使用Certbot免费证书</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1304,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>周末安排值班人员</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1342,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>根据UAT反馈调整</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1381,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>优先级：阻断性 &gt; 一般</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1420,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>准备上线检查清单</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1458,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>上线后首个周末加强监控</t>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -1528,6 +1532,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1568,7 +1573,8 @@
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>高
+已通过</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1596,8 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>低
+已完成（ECS 4核8G + OSS 100G/年）</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1619,8 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>高
+进行中，预计6月13-14日</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1642,8 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中
+预计6月15-16日</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1665,8 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中
+预计6月15日</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1688,8 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中
+已完成</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1711,8 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>高
+预计6月19日</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1734,8 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>高
+预计6月23日</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1757,8 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>高
+预计6月25日</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1780,8 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中
+预计6月30日</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2464,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>🔄 进行中</t>
+          <t>✔ 已完成</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>预计6月6日</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -2557,12 +2572,12 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>🔄 进行中</t>
+          <t>✔ 已完成</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>预计6月6日</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
